--- a/Result/profitability/2903.xlsx
+++ b/Result/profitability/2903.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>0.38375</v>
+        <v>0.36625</v>
       </c>
       <c r="N2" t="n">
-        <v>53.05375</v>
+        <v>53.325</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.33375</v>
+        <v>0.285</v>
       </c>
       <c r="N3" t="n">
-        <v>48.28375</v>
+        <v>49.14</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2775</v>
+        <v>0.255</v>
       </c>
       <c r="N4" t="n">
-        <v>44.1175</v>
+        <v>44.52125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0.23375</v>
+        <v>0.2175</v>
       </c>
       <c r="N5" t="n">
-        <v>39.5375</v>
+        <v>39.48875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.28</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2325</v>
+        <v>0.19125</v>
       </c>
       <c r="N6" t="n">
-        <v>34.5175</v>
+        <v>34.58125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1925</v>
+        <v>0.1575</v>
       </c>
       <c r="N7" t="n">
-        <v>29.595</v>
+        <v>30.3525</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.55</v>
       </c>
       <c r="M8" t="n">
-        <v>0.20625</v>
+        <v>0.1775</v>
       </c>
       <c r="N8" t="n">
-        <v>25.3825</v>
+        <v>25.69625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>0.9</v>
       </c>
       <c r="M13" t="n">
-        <v>0.46625</v>
+        <v>0.4662500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>21.3325</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2903</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7518</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2972</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4546</v>
+      </c>
+      <c r="F75" t="n">
+        <v>60.47</v>
+      </c>
+      <c r="G75" t="n">
+        <v>984</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>13.09%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-260</v>
+      </c>
+      <c r="J75" t="n">
+        <v>725</v>
+      </c>
+      <c r="K75" t="n">
+        <v>225</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N75" t="n">
+        <v>57.85250000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5897435897435898</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.509999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.04330572808833666</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4482758620689654</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.3900000000000006</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.006408149852119682</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
